--- a/artfynd/A 27395-2026 artfynd.xlsx
+++ b/artfynd/A 27395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135528981</v>
       </c>
       <c r="B2" t="n">
-        <v>93379</v>
+        <v>93381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135528984</v>
       </c>
       <c r="B3" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27395-2026 artfynd.xlsx
+++ b/artfynd/A 27395-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135528968</v>
+        <v>135996085</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,20 +945,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fasaskogen öster om Vinterviken, Nrk</t>
+          <t>Vinterviken, Vinterviken, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481542</v>
+        <v>481591</v>
       </c>
       <c r="R4" t="n">
-        <v>6566454</v>
+        <v>6566496</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,12 +991,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,25 +1017,1647 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996085</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135996104</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481546</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6566543</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996104</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135996107</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481617</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6566495</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996107</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135996111</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481575</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6566568</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996111</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135996047</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57629</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>481657</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6566484</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996047</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135996070</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57629</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>481601</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6566451</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996070</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135995957</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57865</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100100</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bivråk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pernis apivorus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481549</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6566549</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135995957</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135995987</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481601</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6566521</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135995987</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135996354</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481559</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6566575</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996354</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135996360</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481549</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6566567</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996360</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135996382</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481579</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6566567</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996382</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135996385</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481559</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6566519</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996385</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135996410</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vinterviken, Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>481529</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6566566</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135996410</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135528968</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fasaskogen öster om Vinterviken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481542</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6566454</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135528968</t>
         </is>
@@ -1030,6 +2668,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27395-2026 artfynd.xlsx
+++ b/artfynd/A 27395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135528981</v>
       </c>
       <c r="B2" t="n">
-        <v>93381</v>
+        <v>93396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135528984</v>
       </c>
       <c r="B3" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135996085</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135996104</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135996107</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>135996111</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>135996047</v>
       </c>
       <c r="B8" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135996070</v>
       </c>
       <c r="B9" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135995957</v>
       </c>
       <c r="B10" t="n">
-        <v>57865</v>
+        <v>57867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135995987</v>
       </c>
       <c r="B11" t="n">
-        <v>58139</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135996354</v>
       </c>
       <c r="B12" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135996360</v>
       </c>
       <c r="B13" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>135996382</v>
       </c>
       <c r="B14" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135996385</v>
       </c>
       <c r="B15" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135996410</v>
       </c>
       <c r="B16" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135528968</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27395-2026 artfynd.xlsx
+++ b/artfynd/A 27395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135528981</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135528984</v>
       </c>
       <c r="B3" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27395-2026 artfynd.xlsx
+++ b/artfynd/A 27395-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135996085</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135996104</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135996107</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>135996111</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>135996047</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135996070</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135995957</v>
       </c>
       <c r="B10" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135995987</v>
       </c>
       <c r="B11" t="n">
-        <v>58141</v>
+        <v>58142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135996354</v>
       </c>
       <c r="B12" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135996360</v>
       </c>
       <c r="B13" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>135996382</v>
       </c>
       <c r="B14" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135996385</v>
       </c>
       <c r="B15" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135996410</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27395-2026 artfynd.xlsx
+++ b/artfynd/A 27395-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135996085</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135996104</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135996107</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>135996111</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>135996047</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>57636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135996070</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>57636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135995957</v>
       </c>
       <c r="B10" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135995987</v>
       </c>
       <c r="B11" t="n">
-        <v>58142</v>
+        <v>58146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135996354</v>
       </c>
       <c r="B12" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135996360</v>
       </c>
       <c r="B13" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>135996382</v>
       </c>
       <c r="B14" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135996385</v>
       </c>
       <c r="B15" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135996410</v>
       </c>
       <c r="B16" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27395-2026 artfynd.xlsx
+++ b/artfynd/A 27395-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135996085</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135996104</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135996107</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>135996111</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>135996047</v>
       </c>
       <c r="B8" t="n">
-        <v>57636</v>
+        <v>57637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135996070</v>
       </c>
       <c r="B9" t="n">
-        <v>57636</v>
+        <v>57637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135995957</v>
       </c>
       <c r="B10" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135995987</v>
       </c>
       <c r="B11" t="n">
-        <v>58146</v>
+        <v>58147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>135996354</v>
       </c>
       <c r="B12" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135996360</v>
       </c>
       <c r="B13" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>135996382</v>
       </c>
       <c r="B14" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135996385</v>
       </c>
       <c r="B15" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135996410</v>
       </c>
       <c r="B16" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
